--- a/31/Data/Datasheet.xlsx
+++ b/31/Data/Datasheet.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Moritz/Documents/GitHub/C-Praktikum/31/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F95A28-B0A5-2642-A7AB-2BFF21CAF1F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8BC8948-84CC-4B47-AE99-6DFB378E74DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3080" yWindow="2060" windowWidth="28040" windowHeight="17440" activeTab="1" xr2:uid="{2137D639-72A8-B642-884A-98A6CE83B14D}"/>
+    <workbookView xWindow="3080" yWindow="2060" windowWidth="28040" windowHeight="17440" xr2:uid="{2137D639-72A8-B642-884A-98A6CE83B14D}"/>
   </bookViews>
   <sheets>
-    <sheet name="T = 35°C" sheetId="3" r:id="rId1"/>
-    <sheet name="T = 45 °C" sheetId="2" r:id="rId2"/>
-    <sheet name="T = 30 °C" sheetId="1" r:id="rId3"/>
+    <sheet name="T = 50°C" sheetId="9" r:id="rId1"/>
+    <sheet name="T = 48°C" sheetId="8" r:id="rId2"/>
+    <sheet name="T = 42°C" sheetId="6" r:id="rId3"/>
+    <sheet name="T = 35°C" sheetId="3" r:id="rId4"/>
+    <sheet name="T = 40°C" sheetId="4" r:id="rId5"/>
+    <sheet name="T = 45 °C" sheetId="2" r:id="rId6"/>
+    <sheet name="T = 30 °C" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="6">
   <si>
     <t>Volumen [ml]</t>
   </si>
@@ -195,26 +199,137 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'T = 35°C'!$B$2:$B$60</c:f>
+              <c:f>'T = 50°C'!$B$2:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>12</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'T = 35°C'!$A$2:$A$60</c:f>
+              <c:f>'T = 50°C'!$A$2:$A$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35.25</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37.75</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>38.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>39.75</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>42</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-41F3-D44C-B6BA-F364CAAD0D20}"/>
+              <c16:uniqueId val="{00000000-DE55-BF4A-8D9D-640D7A5109E9}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -485,6 +600,1658 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
+              <c:f>'T = 48°C'!$B$2:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'T = 48°C'!$A$2:$A$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19.75</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>32.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>37.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>40.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>44.25</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E3C9-4445-8466-775F9331A51F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="747712688"/>
+        <c:axId val="747718096"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="747712688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747718096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="747718096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747712688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>p / V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'T = 42°C'!$B$2:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.22500000000000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'T = 42°C'!$A$2:$A$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>15</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>19</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>27</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>30.75</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>32.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>32.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>32.25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>34</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-85D8-D141-8B45-613D301B7A6A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="747712688"/>
+        <c:axId val="747718096"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="747712688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747718096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="747718096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747712688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>p / V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'T = 35°C'!$B$2:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3.25</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.25</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'T = 35°C'!$A$2:$A$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>7.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.25</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>18</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>25.25</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>26</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>27.5</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>41</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-41F3-D44C-B6BA-F364CAAD0D20}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="747712688"/>
+        <c:axId val="747718096"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="747712688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747718096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="747718096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747712688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>p / V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'T = 40°C'!$B$2:$B$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>3.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.85</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.75</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.7</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.65</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.55000000000000004</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.45</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.4</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0.3</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0.25</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>0.2</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'T = 40°C'!$A$2:$A$60</c:f>
+              <c:numCache>
+                <c:formatCode>0.000</c:formatCode>
+                <c:ptCount val="59"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>14.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>18.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>25</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>27.25</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>30.75</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>43.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-371B-9E46-AD8D-494605BE1259}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="747712688"/>
+        <c:axId val="747718096"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="747712688"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747718096"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="747718096"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.000" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="747712688"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>p / V</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
               <c:f>'T = 45 °C'!$B$2:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
@@ -809,7 +2576,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -1441,6 +3208,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
@@ -2989,20 +4916,2213 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>412750</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>520700</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>292100</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{961B5EF7-3BD9-D54C-8900-20B476B4850D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CFC6D55-FF51-9B46-A620-9B7546702113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{45257625-6244-2540-B09E-41208CEC1AC8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3032,7 +7152,50 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>558800</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CA0B055E-B133-E84F-8929-62E51ACA98AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3075,7 +7238,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3432,8 +7595,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B272A1-088C-BE46-A93E-9B7DA77F9D86}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB87AFE9-E5E1-BC49-9FD3-53F8F39FC020}">
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
@@ -3460,6 +7623,12 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.5</v>
+      </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
       </c>
@@ -3467,7 +7636,148 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="E2" s="2">
-        <v>35</v>
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>10.5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>15.75</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>30</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>32</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>33</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>35.25</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>36.25</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>37</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>37.75</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>38.5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>39</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>39.75</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>42</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="2">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -3477,6 +7787,897 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{350F195C-A403-F54F-8CCC-558D576515B0}">
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="11.83203125" style="2"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="11.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>15.5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>19.75</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>30</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>32.25</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>36</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>36.5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>37</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>37.5</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>40.5</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>44.25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B1AAC5C-95A1-AE41-B929-06FAC14110F6}">
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="11.83203125" style="2"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="11.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>15</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>25.5</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>28.5</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>30</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>30.75</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>31.5</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>32</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>32</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>32</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>32</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>32.25</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>32.25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>32.25</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>34</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97B272A1-088C-BE46-A93E-9B7DA77F9D86}">
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="11.83203125" style="2"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="11.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>7.5</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3.25</v>
+      </c>
+      <c r="E3" s="2">
+        <v>34.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>9</v>
+      </c>
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>11.25</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E5" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>14</v>
+      </c>
+      <c r="B6" s="2">
+        <v>2</v>
+      </c>
+      <c r="E6" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E7" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>21</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="E8" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>24</v>
+      </c>
+      <c r="B9" s="2">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>25.25</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E10" s="2">
+        <v>34.6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>26</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>27.5</v>
+      </c>
+      <c r="B23" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A647D4E1-B06E-CB4B-840E-4F25C8AC2F34}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" style="2" customWidth="1"/>
+    <col min="2" max="3" width="11.83203125" style="2"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="16384" width="11.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>8</v>
+      </c>
+      <c r="B2" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="E2" s="2">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="B3" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>11.5</v>
+      </c>
+      <c r="B4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="E4" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>14.5</v>
+      </c>
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>18.5</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="E6" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>26.5</v>
+      </c>
+      <c r="B8" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="E8" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>27.25</v>
+      </c>
+      <c r="B9" s="2">
+        <v>0.85</v>
+      </c>
+      <c r="E9" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>28</v>
+      </c>
+      <c r="B10" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="E10" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="E11" s="2">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>29.5</v>
+      </c>
+      <c r="B12" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="E12" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>30</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="E13" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B14" s="2">
+        <v>0.6</v>
+      </c>
+      <c r="E14" s="2">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B15" s="2">
+        <v>0.55000000000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B18" s="2">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>30.5</v>
+      </c>
+      <c r="B20" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>30.75</v>
+      </c>
+      <c r="B21" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>43.5</v>
+      </c>
+      <c r="B22" s="2">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CCEC536-AB9D-214B-BA3C-E2A2996E26EF}">
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -3539,6 +8740,9 @@
       <c r="B4" s="2">
         <v>3</v>
       </c>
+      <c r="E4" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="5" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
@@ -3547,6 +8751,9 @@
       <c r="B5" s="2">
         <v>2.75</v>
       </c>
+      <c r="E5" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -3577,6 +8784,9 @@
       <c r="B8" s="2">
         <v>2</v>
       </c>
+      <c r="E8" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
@@ -3585,6 +8795,9 @@
       <c r="B9" s="2">
         <v>1.75</v>
       </c>
+      <c r="E9" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
@@ -3593,6 +8806,9 @@
       <c r="B10" s="2">
         <v>1.5</v>
       </c>
+      <c r="E10" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
@@ -3601,6 +8817,9 @@
       <c r="B11" s="2">
         <v>1.25</v>
       </c>
+      <c r="E11" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
@@ -3609,6 +8828,9 @@
       <c r="B12" s="2">
         <v>1</v>
       </c>
+      <c r="E12" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="13" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
@@ -3617,6 +8839,9 @@
       <c r="B13" s="2">
         <v>0.75</v>
       </c>
+      <c r="E13" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="14" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
@@ -3625,6 +8850,9 @@
       <c r="B14" s="2">
         <v>0.5</v>
       </c>
+      <c r="E14" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="15" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
@@ -3633,6 +8861,9 @@
       <c r="B15" s="2">
         <v>0.45</v>
       </c>
+      <c r="E15" s="2">
+        <v>44.5</v>
+      </c>
     </row>
     <row r="16" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
@@ -3641,37 +8872,52 @@
       <c r="B16" s="2">
         <v>0.4</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E16" s="2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>34.5</v>
       </c>
       <c r="B17" s="2">
         <v>0.35</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E17" s="2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>34.5</v>
       </c>
       <c r="B18" s="2">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E18" s="2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>35.5</v>
       </c>
       <c r="B19" s="2">
         <v>0.25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E19" s="2">
+        <v>44.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>40</v>
       </c>
       <c r="B20" s="2">
         <v>0.22500000000000001</v>
+      </c>
+      <c r="E20" s="2">
+        <v>44.5</v>
       </c>
     </row>
   </sheetData>
@@ -3680,7 +8926,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE61DF27-4FB3-AD4D-9363-53574DA6DFF9}">
   <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.83203125" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -4041,6 +9287,9 @@
       <c r="B31" s="1">
         <v>0.55000000000000004</v>
       </c>
+      <c r="E31" s="1">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
@@ -4049,6 +9298,9 @@
       <c r="B32" s="1">
         <v>0.5</v>
       </c>
+      <c r="E32" s="1">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
@@ -4057,6 +9309,9 @@
       <c r="B33" s="1">
         <v>0.45</v>
       </c>
+      <c r="E33" s="1">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="34" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
@@ -4087,6 +9342,9 @@
       <c r="B36" s="1">
         <v>0.3</v>
       </c>
+      <c r="E36" s="1">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="37" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
@@ -4095,6 +9353,9 @@
       <c r="B37" s="1">
         <v>0.25</v>
       </c>
+      <c r="E37" s="1">
+        <v>29.6</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
@@ -4102,6 +9363,9 @@
       </c>
       <c r="B38" s="1">
         <v>0.2</v>
+      </c>
+      <c r="E38" s="1">
+        <v>29.6</v>
       </c>
     </row>
   </sheetData>
